--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:33:22+00:00</t>
+    <t>2026-04-24T13:15:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T13:15:59+00:00</t>
+    <t>2026-04-29T08:17:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,11 +269,11 @@
     <t>fr-lm-allergy-intolerance.header.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient
 </t>
   </si>
   <si>
-    <t>Patient/subject information</t>
+    <t>Patient / Usager</t>
   </si>
   <si>
     <t>fr-lm-entry.header.subject</t>
@@ -443,7 +443,7 @@
     <t>fr-lm-entry.header.source</t>
   </si>
   <si>
-    <t>fr-lm-allergy-intolerance.header.langue</t>
+    <t>fr-lm-allergy-intolerance.header.language</t>
   </si>
   <si>
     <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
@@ -451,7 +451,7 @@
 La partie en majuscules indique le code pays (ISO-3166)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.langue</t>
+    <t>fr-lm-entry.header.language</t>
   </si>
   <si>
     <t>fr-lm-allergy-intolerance.type</t>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1410" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1379" uniqueCount="216">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:17:29+00:00</t>
+    <t>2026-04-29T08:41:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -422,13 +422,16 @@
 </t>
   </si>
   <si>
-    <t>Statut de l'acte</t>
-  </si>
-  <si>
-    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+    <t>Statut clinique de l'allergie</t>
+  </si>
+  <si>
+    <t>Statut</t>
+  </si>
+  <si>
+    <t>jdv-hl7-allergyintolerance-clinical-cisis (2.16.840.1.113883.4.642.3.1372)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-allergyintolerance-clinical-cisis</t>
   </si>
   <si>
     <t>fr-lm-entry.header.status</t>
@@ -494,18 +497,6 @@
   </si>
   <si>
     <t>commentaire</t>
-  </si>
-  <si>
-    <t>fr-lm-allergy-intolerance.clinicalStatus</t>
-  </si>
-  <si>
-    <t>Statut clinique de l'allergie</t>
-  </si>
-  <si>
-    <t>jdv-hl7-allergyintolerance-clinical-cisis (2.16.840.1.113883.4.642.3.1372)</t>
-  </si>
-  <si>
-    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-allergyintolerance-clinical-cisis</t>
   </si>
   <si>
     <t>fr-lm-allergy-intolerance.criticality</t>
@@ -999,7 +990,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ44"/>
+  <dimension ref="A1:AJ43"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="56.32421875" customWidth="true" bestFit="true"/>
@@ -2662,7 +2653,7 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G17" t="s" s="2">
         <v>79</v>
@@ -2683,7 +2674,7 @@
         <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2713,10 +2704,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2734,10 +2725,10 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH17" t="s" s="2">
         <v>79</v>
@@ -2751,10 +2742,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2780,10 +2771,10 @@
         <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2834,7 +2825,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2851,10 +2842,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2880,10 +2871,10 @@
         <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2934,7 +2925,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2951,10 +2942,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2980,10 +2971,10 @@
         <v>131</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -3013,10 +3004,10 @@
         <v>73</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>73</v>
@@ -3034,7 +3025,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>79</v>
@@ -3051,10 +3042,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3080,10 +3071,10 @@
         <v>131</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3113,7 +3104,7 @@
         <v>73</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="Z21" t="s" s="2">
         <v>73</v>
@@ -3134,7 +3125,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3151,10 +3142,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3180,10 +3171,10 @@
         <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3234,7 +3225,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>79</v>
@@ -3251,10 +3242,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3277,13 +3268,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3334,7 +3325,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3351,10 +3342,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3380,10 +3371,10 @@
         <v>131</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3413,10 +3404,10 @@
         <v>73</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>73</v>
@@ -3434,7 +3425,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>74</v>
@@ -3451,10 +3442,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3480,10 +3471,10 @@
         <v>131</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3513,10 +3504,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3534,7 +3525,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3551,10 +3542,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3562,7 +3553,7 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G26" t="s" s="2">
         <v>79</v>
@@ -3577,13 +3568,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3613,10 +3604,10 @@
         <v>73</v>
       </c>
       <c r="Y26" t="s" s="2">
-        <v>164</v>
+        <v>73</v>
       </c>
       <c r="Z26" t="s" s="2">
-        <v>165</v>
+        <v>73</v>
       </c>
       <c r="AA26" t="s" s="2">
         <v>73</v>
@@ -3634,10 +3625,10 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH26" t="s" s="2">
         <v>79</v>
@@ -3646,15 +3637,15 @@
         <v>73</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3662,7 +3653,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>79</v>
@@ -3677,13 +3668,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L27" t="s" s="2">
         <v>168</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3734,10 +3725,10 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>79</v>
@@ -3746,26 +3737,26 @@
         <v>73</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>73</v>
@@ -3777,15 +3768,17 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N28" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N28" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>73</v>
@@ -3822,50 +3815,50 @@
         <v>73</v>
       </c>
       <c r="AB28" t="s" s="2">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="AC28" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AD28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE28" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>73</v>
@@ -3877,16 +3870,16 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -3924,39 +3917,39 @@
         <v>73</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3964,7 +3957,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>79</v>
@@ -3979,17 +3972,15 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>73</v>
@@ -4038,10 +4029,10 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>79</v>
@@ -4050,15 +4041,15 @@
         <v>73</v>
       </c>
       <c r="AJ30" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4081,13 +4072,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4138,7 +4129,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4150,15 +4141,15 @@
         <v>73</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>195</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4184,10 +4175,10 @@
         <v>127</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4238,7 +4229,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4255,10 +4246,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4269,7 +4260,7 @@
         <v>74</v>
       </c>
       <c r="G33" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H33" t="s" s="2">
         <v>73</v>
@@ -4281,13 +4272,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>127</v>
+        <v>80</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4338,13 +4329,13 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>73</v>
@@ -4355,10 +4346,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4369,7 +4360,7 @@
         <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4381,13 +4372,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>80</v>
+        <v>131</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4417,7 +4408,7 @@
         <v>73</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>73</v>
+        <v>201</v>
       </c>
       <c r="Z34" t="s" s="2">
         <v>73</v>
@@ -4438,13 +4429,13 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
@@ -4466,7 +4457,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>79</v>
@@ -4541,7 +4532,7 @@
         <v>202</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>79</v>
@@ -4566,7 +4557,7 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G36" t="s" s="2">
         <v>79</v>
@@ -4620,7 +4611,7 @@
         <v>207</v>
       </c>
       <c r="Z36" t="s" s="2">
-        <v>73</v>
+        <v>208</v>
       </c>
       <c r="AA36" t="s" s="2">
         <v>73</v>
@@ -4641,7 +4632,7 @@
         <v>205</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH36" t="s" s="2">
         <v>79</v>
@@ -4655,10 +4646,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4666,7 +4657,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>79</v>
@@ -4681,13 +4672,13 @@
         <v>73</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>131</v>
+        <v>164</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -4717,10 +4708,10 @@
         <v>73</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>210</v>
+        <v>73</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>211</v>
+        <v>73</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>73</v>
@@ -4738,10 +4729,10 @@
         <v>73</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>79</v>
@@ -4750,15 +4741,15 @@
         <v>73</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -4766,7 +4757,7 @@
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G38" t="s" s="2">
         <v>79</v>
@@ -4781,13 +4772,13 @@
         <v>73</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>167</v>
+        <v>153</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>168</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -4838,10 +4829,10 @@
         <v>73</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>212</v>
+        <v>170</v>
       </c>
       <c r="AG38" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH38" t="s" s="2">
         <v>79</v>
@@ -4850,26 +4841,26 @@
         <v>73</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
-        <v>73</v>
+        <v>172</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="G39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H39" t="s" s="2">
         <v>73</v>
@@ -4881,15 +4872,17 @@
         <v>73</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>152</v>
+        <v>173</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>172</v>
-      </c>
-      <c r="N39" s="2"/>
+        <v>175</v>
+      </c>
+      <c r="N39" t="s" s="2">
+        <v>176</v>
+      </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
         <v>73</v>
@@ -4926,50 +4919,50 @@
         <v>73</v>
       </c>
       <c r="AB39" t="s" s="2">
-        <v>73</v>
+        <v>177</v>
       </c>
       <c r="AC39" t="s" s="2">
-        <v>73</v>
+        <v>178</v>
       </c>
       <c r="AD39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE39" t="s" s="2">
-        <v>73</v>
+        <v>179</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI39" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
-        <v>175</v>
+        <v>73</v>
       </c>
       <c r="E40" s="2"/>
       <c r="F40" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>73</v>
@@ -4981,16 +4974,16 @@
         <v>73</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5028,39 +5021,39 @@
         <v>73</v>
       </c>
       <c r="AB40" t="s" s="2">
-        <v>180</v>
+        <v>73</v>
       </c>
       <c r="AC40" t="s" s="2">
-        <v>181</v>
+        <v>73</v>
       </c>
       <c r="AD40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AE40" t="s" s="2">
-        <v>182</v>
+        <v>73</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AG40" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH40" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI40" t="s" s="2">
         <v>73</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5068,7 +5061,7 @@
       </c>
       <c r="E41" s="2"/>
       <c r="F41" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G41" t="s" s="2">
         <v>79</v>
@@ -5083,17 +5076,15 @@
         <v>73</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>187</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>188</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="N41" s="2"/>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
         <v>73</v>
@@ -5142,10 +5133,10 @@
         <v>73</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG41" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH41" t="s" s="2">
         <v>79</v>
@@ -5154,15 +5145,15 @@
         <v>73</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>73</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -5185,13 +5176,13 @@
         <v>73</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>191</v>
+        <v>127</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -5242,7 +5233,7 @@
         <v>73</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>194</v>
+        <v>214</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>74</v>
@@ -5254,15 +5245,15 @@
         <v>73</v>
       </c>
       <c r="AJ42" t="s" s="2">
-        <v>195</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -5288,10 +5279,10 @@
         <v>127</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -5342,7 +5333,7 @@
         <v>73</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>74</v>
@@ -5354,106 +5345,6 @@
         <v>73</v>
       </c>
       <c r="AJ43" t="s" s="2">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>127</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>218</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
+++ b/fusionModeleLogique/ig/StructureDefinition-fr-lm-allergy-intolerance.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-29T08:41:15+00:00</t>
+    <t>2026-04-30T08:29:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
